--- a/2025_10_06_LACV_50N_no_NSs_exp1/data/LACV_50N_no_NSs_exp1_normalized_data.xlsx
+++ b/2025_10_06_LACV_50N_no_NSs_exp1/data/LACV_50N_no_NSs_exp1_normalized_data.xlsx
@@ -1694,7 +1694,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Trvittatus</t>
+          <t>Trivittatus</t>
         </is>
       </c>
       <c r="B54">
